--- a/hardware/boards/brain/PickAndPlace_brain.xlsx
+++ b/hardware/boards/brain/PickAndPlace_brain.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB_2026_07_20" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_brain_2026_09_13" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="483">
   <si>
     <t>Designator</t>
   </si>
@@ -1291,145 +1291,175 @@
     <t>-14.986mm</t>
   </si>
   <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>-28.194mm</t>
+  </si>
+  <si>
+    <t>-12.954mm</t>
+  </si>
+  <si>
+    <t>-27.761mm</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>GRM155R71H104KE14D</t>
+  </si>
+  <si>
+    <t>-11.747mm</t>
+  </si>
+  <si>
+    <t>-8.052mm</t>
+  </si>
+  <si>
+    <t>-11.441mm</t>
+  </si>
+  <si>
+    <t>-8.358mm</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>-2.108mm</t>
+  </si>
+  <si>
+    <t>-9.576mm</t>
+  </si>
+  <si>
+    <t>-1.675mm</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>-6.96mm</t>
+  </si>
+  <si>
+    <t>-5.512mm</t>
+  </si>
+  <si>
+    <t>-5.079mm</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>-12.192mm</t>
+  </si>
+  <si>
+    <t>-12.625mm</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>-4.138mm</t>
+  </si>
+  <si>
+    <t>-16.18mm</t>
+  </si>
+  <si>
+    <t>-15.747mm</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>CL05A105KP5NNNC</t>
+  </si>
+  <si>
+    <t>-27.94mm</t>
+  </si>
+  <si>
+    <t>-13.133mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>CL05C100JB5NNNC</t>
+  </si>
+  <si>
+    <t>-5.055mm</t>
+  </si>
+  <si>
+    <t>10pF</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>-5.076mm</t>
+  </si>
+  <si>
+    <t>-7.341mm</t>
+  </si>
+  <si>
+    <t>-6.908mm</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>-12.509mm</t>
+  </si>
+  <si>
+    <t>-6.337mm</t>
+  </si>
+  <si>
+    <t>-12.203mm</t>
+  </si>
+  <si>
+    <t>-6.031mm</t>
+  </si>
+  <si>
     <t>R5</t>
   </si>
   <si>
-    <t>-30.734mm</t>
-  </si>
-  <si>
-    <t>-12.954mm</t>
-  </si>
-  <si>
-    <t>-30.301mm</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>-28.194mm</t>
-  </si>
-  <si>
-    <t>-27.761mm</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>GRM155R71H104KE14D</t>
-  </si>
-  <si>
-    <t>-11.747mm</t>
-  </si>
-  <si>
-    <t>-8.052mm</t>
-  </si>
-  <si>
-    <t>-11.441mm</t>
-  </si>
-  <si>
-    <t>-8.358mm</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>-2.108mm</t>
-  </si>
-  <si>
-    <t>-9.576mm</t>
-  </si>
-  <si>
-    <t>-1.675mm</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>-6.96mm</t>
-  </si>
-  <si>
-    <t>-5.512mm</t>
-  </si>
-  <si>
-    <t>-5.079mm</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>-12.192mm</t>
-  </si>
-  <si>
-    <t>-12.625mm</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>-4.138mm</t>
-  </si>
-  <si>
-    <t>-16.18mm</t>
-  </si>
-  <si>
-    <t>-15.747mm</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>CL05A105KP5NNNC</t>
-  </si>
-  <si>
-    <t>-27.94mm</t>
-  </si>
-  <si>
-    <t>-13.133mm</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>CL05C100JB5NNNC</t>
-  </si>
-  <si>
-    <t>-5.055mm</t>
-  </si>
-  <si>
-    <t>10pF</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>-5.076mm</t>
-  </si>
-  <si>
-    <t>-7.341mm</t>
-  </si>
-  <si>
-    <t>-6.908mm</t>
-  </si>
-  <si>
-    <t>C50</t>
-  </si>
-  <si>
-    <t>-12.509mm</t>
-  </si>
-  <si>
-    <t>-6.337mm</t>
-  </si>
-  <si>
-    <t>-12.203mm</t>
-  </si>
-  <si>
-    <t>-6.031mm</t>
+    <t>-29.718mm</t>
+  </si>
+  <si>
+    <t>-11.684mm</t>
+  </si>
+  <si>
+    <t>-29.285mm</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>-33.528mm</t>
+  </si>
+  <si>
+    <t>-33.961mm</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>SN74AHCT1G125DBVR(UMW)</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L3.0-W1.5-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>-32.766mm</t>
+  </si>
+  <si>
+    <t>-31.516mm</t>
+  </si>
+  <si>
+    <t>-12.634mm</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -5912,19 +5942,19 @@
         <v>91</v>
       </c>
       <c r="D88" t="s">
-        <v>431</v>
+        <v>127</v>
       </c>
       <c r="E88" t="s">
         <v>428</v>
       </c>
       <c r="F88" t="s">
-        <v>431</v>
+        <v>127</v>
       </c>
       <c r="G88" t="s">
         <v>428</v>
       </c>
       <c r="H88" t="s">
-        <v>432</v>
+        <v>128</v>
       </c>
       <c r="I88" t="s">
         <v>428</v>
@@ -5950,31 +5980,31 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="C89" t="s">
         <v>91</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
+        <v>433</v>
       </c>
       <c r="E89" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F89" t="s">
-        <v>127</v>
+        <v>433</v>
       </c>
       <c r="G89" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="H89" t="s">
-        <v>128</v>
+        <v>435</v>
       </c>
       <c r="I89" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="J89">
         <v>2</v>
@@ -5983,42 +6013,42 @@
         <v>22</v>
       </c>
       <c r="L89">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="M89" t="s">
         <v>23</v>
       </c>
       <c r="N89" t="s">
-        <v>253</v>
+        <v>52</v>
       </c>
       <c r="O89" t="s">
-        <v>253</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B90" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C90" t="s">
         <v>91</v>
       </c>
       <c r="D90" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E90" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F90" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G90" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H90" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I90" t="s">
         <v>439</v>
@@ -6030,7 +6060,7 @@
         <v>22</v>
       </c>
       <c r="L90">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="M90" t="s">
         <v>23</v>
@@ -6044,31 +6074,31 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B91" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C91" t="s">
         <v>91</v>
       </c>
       <c r="D91" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E91" t="s">
+        <v>443</v>
+      </c>
+      <c r="F91" t="s">
         <v>442</v>
       </c>
-      <c r="F91" t="s">
-        <v>441</v>
-      </c>
       <c r="G91" t="s">
+        <v>443</v>
+      </c>
+      <c r="H91" t="s">
         <v>442</v>
       </c>
-      <c r="H91" t="s">
-        <v>443</v>
-      </c>
       <c r="I91" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J91">
         <v>2</v>
@@ -6077,7 +6107,7 @@
         <v>22</v>
       </c>
       <c r="L91">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M91" t="s">
         <v>23</v>
@@ -6091,31 +6121,31 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B92" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C92" t="s">
         <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E92" t="s">
+        <v>425</v>
+      </c>
+      <c r="F92" t="s">
         <v>446</v>
       </c>
-      <c r="F92" t="s">
-        <v>445</v>
-      </c>
       <c r="G92" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="H92" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I92" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="J92">
         <v>2</v>
@@ -6124,7 +6154,7 @@
         <v>22</v>
       </c>
       <c r="L92">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M92" t="s">
         <v>23</v>
@@ -6141,7 +6171,7 @@
         <v>448</v>
       </c>
       <c r="B93" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C93" t="s">
         <v>91</v>
@@ -6150,19 +6180,19 @@
         <v>449</v>
       </c>
       <c r="E93" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="F93" t="s">
         <v>449</v>
       </c>
       <c r="G93" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="H93" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I93" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="J93">
         <v>2</v>
@@ -6171,7 +6201,7 @@
         <v>22</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M93" t="s">
         <v>23</v>
@@ -6185,28 +6215,28 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B94" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="C94" t="s">
         <v>91</v>
       </c>
       <c r="D94" t="s">
-        <v>452</v>
+        <v>114</v>
       </c>
       <c r="E94" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F94" t="s">
-        <v>452</v>
+        <v>114</v>
       </c>
       <c r="G94" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H94" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I94" t="s">
         <v>454</v>
@@ -6218,45 +6248,45 @@
         <v>22</v>
       </c>
       <c r="L94">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M94" t="s">
         <v>23</v>
       </c>
       <c r="N94" t="s">
-        <v>52</v>
+        <v>456</v>
       </c>
       <c r="O94" t="s">
-        <v>52</v>
+        <v>456</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B95" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C95" t="s">
         <v>91</v>
       </c>
       <c r="D95" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="E95" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F95" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="G95" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H95" t="s">
-        <v>458</v>
+        <v>187</v>
       </c>
       <c r="I95" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J95">
         <v>2</v>
@@ -6271,39 +6301,39 @@
         <v>23</v>
       </c>
       <c r="N95" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O95" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B96" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C96" t="s">
         <v>91</v>
       </c>
       <c r="D96" t="s">
-        <v>185</v>
+        <v>462</v>
       </c>
       <c r="E96" t="s">
+        <v>463</v>
+      </c>
+      <c r="F96" t="s">
         <v>462</v>
       </c>
-      <c r="F96" t="s">
-        <v>185</v>
-      </c>
       <c r="G96" t="s">
+        <v>463</v>
+      </c>
+      <c r="H96" t="s">
         <v>462</v>
       </c>
-      <c r="H96" t="s">
-        <v>187</v>
-      </c>
       <c r="I96" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J96">
         <v>2</v>
@@ -6312,45 +6342,45 @@
         <v>22</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M96" t="s">
         <v>23</v>
       </c>
       <c r="N96" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="O96" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B97" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C97" t="s">
         <v>91</v>
       </c>
       <c r="D97" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E97" t="s">
+        <v>467</v>
+      </c>
+      <c r="F97" t="s">
         <v>466</v>
       </c>
-      <c r="F97" t="s">
-        <v>465</v>
-      </c>
       <c r="G97" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H97" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I97" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -6359,42 +6389,42 @@
         <v>22</v>
       </c>
       <c r="L97">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="M97" t="s">
         <v>23</v>
       </c>
       <c r="N97" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="O97" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B98" t="s">
-        <v>456</v>
+        <v>250</v>
       </c>
       <c r="C98" t="s">
         <v>91</v>
       </c>
       <c r="D98" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E98" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F98" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G98" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H98" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I98" t="s">
         <v>472</v>
@@ -6406,16 +6436,110 @@
         <v>22</v>
       </c>
       <c r="L98">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="M98" t="s">
         <v>23</v>
       </c>
       <c r="N98" t="s">
-        <v>459</v>
+        <v>253</v>
       </c>
       <c r="O98" t="s">
-        <v>459</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>474</v>
+      </c>
+      <c r="B99" t="s">
+        <v>250</v>
+      </c>
+      <c r="C99" t="s">
+        <v>91</v>
+      </c>
+      <c r="D99" t="s">
+        <v>475</v>
+      </c>
+      <c r="E99" t="s">
+        <v>247</v>
+      </c>
+      <c r="F99" t="s">
+        <v>475</v>
+      </c>
+      <c r="G99" t="s">
+        <v>247</v>
+      </c>
+      <c r="H99" t="s">
+        <v>476</v>
+      </c>
+      <c r="I99" t="s">
+        <v>247</v>
+      </c>
+      <c r="J99">
+        <v>2</v>
+      </c>
+      <c r="K99" t="s">
+        <v>22</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99" t="s">
+        <v>23</v>
+      </c>
+      <c r="N99" t="s">
+        <v>253</v>
+      </c>
+      <c r="O99" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>477</v>
+      </c>
+      <c r="B100" t="s">
+        <v>478</v>
+      </c>
+      <c r="C100" t="s">
+        <v>479</v>
+      </c>
+      <c r="D100" t="s">
+        <v>480</v>
+      </c>
+      <c r="E100" t="s">
+        <v>472</v>
+      </c>
+      <c r="F100" t="s">
+        <v>480</v>
+      </c>
+      <c r="G100" t="s">
+        <v>472</v>
+      </c>
+      <c r="H100" t="s">
+        <v>481</v>
+      </c>
+      <c r="I100" t="s">
+        <v>482</v>
+      </c>
+      <c r="J100">
+        <v>5</v>
+      </c>
+      <c r="K100" t="s">
+        <v>22</v>
+      </c>
+      <c r="L100">
+        <v>90</v>
+      </c>
+      <c r="M100" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" t="s">
+        <v>478</v>
+      </c>
+      <c r="O100" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/hardware/boards/brain/PickAndPlace_brain.xlsx
+++ b/hardware/boards/brain/PickAndPlace_brain.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="487">
   <si>
     <t>Designator</t>
   </si>
@@ -775,27 +775,6 @@
     <t>220Ω</t>
   </si>
   <si>
-    <t>U26</t>
-  </si>
-  <si>
-    <t>NCV68061SNAIT1G</t>
-  </si>
-  <si>
-    <t>TSOP-6_L3.0-W1.5-P0.95-BL</t>
-  </si>
-  <si>
-    <t>-23.579mm</t>
-  </si>
-  <si>
-    <t>-28.868mm</t>
-  </si>
-  <si>
-    <t>-22.432mm</t>
-  </si>
-  <si>
-    <t>-29.818mm</t>
-  </si>
-  <si>
     <t>U27</t>
   </si>
   <si>
@@ -1460,6 +1439,39 @@
   </si>
   <si>
     <t>-12.634mm</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>-23.114mm</t>
+  </si>
+  <si>
+    <t>-26.416mm</t>
+  </si>
+  <si>
+    <t>-22.414mm</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>LM74700QDBVRQ1_C2941042</t>
+  </si>
+  <si>
+    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>-24.13mm</t>
+  </si>
+  <si>
+    <t>-22.981mm</t>
+  </si>
+  <si>
+    <t>-29.652mm</t>
+  </si>
+  <si>
+    <t>LM74700QDBVRQ1</t>
   </si>
 </sst>
 </file>
@@ -1836,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -3971,28 +3983,28 @@
         <v>257</v>
       </c>
       <c r="E46" t="s">
-        <v>258</v>
+        <v>122</v>
       </c>
       <c r="F46" t="s">
         <v>257</v>
       </c>
       <c r="G46" t="s">
+        <v>122</v>
+      </c>
+      <c r="H46" t="s">
         <v>258</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>259</v>
       </c>
-      <c r="I46" t="s">
-        <v>260</v>
-      </c>
       <c r="J46">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K46" t="s">
         <v>22</v>
       </c>
       <c r="L46">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
@@ -4006,25 +4018,25 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>260</v>
+      </c>
+      <c r="B47" t="s">
         <v>261</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>262</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>263</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>264</v>
       </c>
-      <c r="E47" t="s">
-        <v>122</v>
-      </c>
       <c r="F47" t="s">
+        <v>263</v>
+      </c>
+      <c r="G47" t="s">
         <v>264</v>
-      </c>
-      <c r="G47" t="s">
-        <v>122</v>
       </c>
       <c r="H47" t="s">
         <v>265</v>
@@ -4033,54 +4045,54 @@
         <v>266</v>
       </c>
       <c r="J47">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K47" t="s">
         <v>22</v>
       </c>
       <c r="L47">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
       </c>
       <c r="N47" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="O47" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E48" t="s">
+        <v>272</v>
+      </c>
+      <c r="F48" t="s">
         <v>271</v>
       </c>
-      <c r="F48" t="s">
-        <v>270</v>
-      </c>
       <c r="G48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H48" t="s">
+        <v>273</v>
+      </c>
+      <c r="I48" t="s">
         <v>272</v>
       </c>
-      <c r="I48" t="s">
-        <v>273</v>
-      </c>
       <c r="J48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48" t="s">
         <v>22</v>
@@ -4092,39 +4104,39 @@
         <v>23</v>
       </c>
       <c r="N48" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="O48" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" t="s">
         <v>275</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>276</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>277</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
+        <v>127</v>
+      </c>
+      <c r="F49" t="s">
+        <v>277</v>
+      </c>
+      <c r="G49" t="s">
+        <v>127</v>
+      </c>
+      <c r="H49" t="s">
         <v>278</v>
       </c>
-      <c r="E49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F49" t="s">
-        <v>278</v>
-      </c>
-      <c r="G49" t="s">
-        <v>279</v>
-      </c>
-      <c r="H49" t="s">
-        <v>280</v>
-      </c>
       <c r="I49" t="s">
-        <v>279</v>
+        <v>127</v>
       </c>
       <c r="J49">
         <v>2</v>
@@ -4139,36 +4151,36 @@
         <v>23</v>
       </c>
       <c r="N49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B50" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C50" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D50" t="s">
-        <v>284</v>
+        <v>190</v>
       </c>
       <c r="E50" t="s">
         <v>127</v>
       </c>
       <c r="F50" t="s">
-        <v>284</v>
+        <v>190</v>
       </c>
       <c r="G50" t="s">
         <v>127</v>
       </c>
       <c r="H50" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I50" t="s">
         <v>127</v>
@@ -4186,57 +4198,57 @@
         <v>23</v>
       </c>
       <c r="N50" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="O50" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B51" t="s">
         <v>282</v>
       </c>
       <c r="C51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" t="s">
         <v>283</v>
       </c>
-      <c r="D51" t="s">
-        <v>190</v>
-      </c>
       <c r="E51" t="s">
-        <v>127</v>
+        <v>284</v>
       </c>
       <c r="F51" t="s">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="G51" t="s">
-        <v>127</v>
+        <v>284</v>
       </c>
       <c r="H51" t="s">
+        <v>285</v>
+      </c>
+      <c r="I51" t="s">
+        <v>286</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51" t="s">
+        <v>22</v>
+      </c>
+      <c r="L51">
+        <v>315</v>
+      </c>
+      <c r="M51" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" t="s">
         <v>287</v>
       </c>
-      <c r="I51" t="s">
-        <v>127</v>
-      </c>
-      <c r="J51">
-        <v>2</v>
-      </c>
-      <c r="K51" t="s">
-        <v>22</v>
-      </c>
-      <c r="L51">
-        <v>180</v>
-      </c>
-      <c r="M51" t="s">
-        <v>23</v>
-      </c>
-      <c r="N51" t="s">
-        <v>282</v>
-      </c>
       <c r="O51" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -4244,29 +4256,29 @@
         <v>288</v>
       </c>
       <c r="B52" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" t="s">
+        <v>196</v>
+      </c>
+      <c r="E52" t="s">
         <v>289</v>
       </c>
-      <c r="C52" t="s">
-        <v>91</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
+        <v>196</v>
+      </c>
+      <c r="G52" t="s">
+        <v>289</v>
+      </c>
+      <c r="H52" t="s">
+        <v>196</v>
+      </c>
+      <c r="I52" t="s">
         <v>290</v>
       </c>
-      <c r="E52" t="s">
-        <v>291</v>
-      </c>
-      <c r="F52" t="s">
-        <v>290</v>
-      </c>
-      <c r="G52" t="s">
-        <v>291</v>
-      </c>
-      <c r="H52" t="s">
-        <v>292</v>
-      </c>
-      <c r="I52" t="s">
-        <v>293</v>
-      </c>
       <c r="J52">
         <v>2</v>
       </c>
@@ -4274,139 +4286,139 @@
         <v>22</v>
       </c>
       <c r="L52">
-        <v>315</v>
+        <v>270</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
       </c>
       <c r="N52" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="O52" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="D53" t="s">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="E53" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F53" t="s">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="G53" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H53" t="s">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="I53" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K53" t="s">
         <v>22</v>
       </c>
       <c r="L53">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="N53" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="O53" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>295</v>
+      </c>
+      <c r="B54" t="s">
+        <v>296</v>
+      </c>
+      <c r="C54" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" t="s">
+        <v>297</v>
+      </c>
+      <c r="E54" t="s">
+        <v>289</v>
+      </c>
+      <c r="F54" t="s">
+        <v>297</v>
+      </c>
+      <c r="G54" t="s">
+        <v>289</v>
+      </c>
+      <c r="H54" t="s">
+        <v>297</v>
+      </c>
+      <c r="I54" t="s">
         <v>298</v>
       </c>
-      <c r="B54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C54" t="s">
-        <v>213</v>
-      </c>
-      <c r="D54" t="s">
-        <v>299</v>
-      </c>
-      <c r="E54" t="s">
-        <v>300</v>
-      </c>
-      <c r="F54" t="s">
-        <v>299</v>
-      </c>
-      <c r="G54" t="s">
-        <v>300</v>
-      </c>
-      <c r="H54" t="s">
-        <v>301</v>
-      </c>
-      <c r="I54" t="s">
-        <v>300</v>
-      </c>
       <c r="J54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K54" t="s">
         <v>22</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M54" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N54" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="O54" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B55" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C55" t="s">
         <v>84</v>
       </c>
       <c r="D55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E55" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G55" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H55" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I55" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -4415,7 +4427,7 @@
         <v>22</v>
       </c>
       <c r="L55">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M55" t="s">
         <v>23</v>
@@ -4429,78 +4441,78 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>303</v>
+      </c>
+      <c r="B56" t="s">
+        <v>304</v>
+      </c>
+      <c r="C56" t="s">
+        <v>305</v>
+      </c>
+      <c r="D56" t="s">
         <v>306</v>
       </c>
-      <c r="B56" t="s">
-        <v>303</v>
-      </c>
-      <c r="C56" t="s">
-        <v>84</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>307</v>
       </c>
-      <c r="E56" t="s">
-        <v>308</v>
-      </c>
       <c r="F56" t="s">
+        <v>306</v>
+      </c>
+      <c r="G56" t="s">
         <v>307</v>
       </c>
-      <c r="G56" t="s">
-        <v>308</v>
-      </c>
       <c r="H56" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I56" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K56" t="s">
         <v>22</v>
       </c>
       <c r="L56">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="N56" t="s">
-        <v>52</v>
+        <v>304</v>
       </c>
       <c r="O56" t="s">
-        <v>52</v>
+        <v>304</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B57" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C57" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E57" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F57" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G57" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="H57" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I57" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -4515,39 +4527,39 @@
         <v>38</v>
       </c>
       <c r="N57" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O57" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C58" t="s">
+        <v>305</v>
+      </c>
+      <c r="D58" t="s">
         <v>311</v>
       </c>
-      <c r="C58" t="s">
+      <c r="E58" t="s">
         <v>312</v>
       </c>
-      <c r="D58" t="s">
-        <v>316</v>
-      </c>
-      <c r="E58" t="s">
-        <v>314</v>
-      </c>
       <c r="F58" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="G58" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H58" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="I58" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -4562,39 +4574,39 @@
         <v>38</v>
       </c>
       <c r="N58" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O58" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B59" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C59" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E59" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F59" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G59" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H59" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I59" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -4609,39 +4621,39 @@
         <v>38</v>
       </c>
       <c r="N59" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O59" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B60" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C60" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E60" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F60" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G60" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="H60" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I60" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -4656,57 +4668,57 @@
         <v>38</v>
       </c>
       <c r="N60" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="O60" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>318</v>
+      </c>
+      <c r="B61" t="s">
+        <v>319</v>
+      </c>
+      <c r="C61" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" t="s">
+        <v>320</v>
+      </c>
+      <c r="E61" t="s">
+        <v>321</v>
+      </c>
+      <c r="F61" t="s">
+        <v>320</v>
+      </c>
+      <c r="G61" t="s">
+        <v>321</v>
+      </c>
+      <c r="H61" t="s">
+        <v>322</v>
+      </c>
+      <c r="I61" t="s">
         <v>323</v>
       </c>
-      <c r="B61" t="s">
-        <v>311</v>
-      </c>
-      <c r="C61" t="s">
-        <v>312</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="J61">
+        <v>3</v>
+      </c>
+      <c r="K61" t="s">
+        <v>22</v>
+      </c>
+      <c r="L61">
+        <v>90</v>
+      </c>
+      <c r="M61" t="s">
+        <v>23</v>
+      </c>
+      <c r="N61" t="s">
         <v>324</v>
       </c>
-      <c r="E61" t="s">
-        <v>322</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="O61" t="s">
         <v>324</v>
-      </c>
-      <c r="G61" t="s">
-        <v>322</v>
-      </c>
-      <c r="H61" t="s">
-        <v>324</v>
-      </c>
-      <c r="I61" t="s">
-        <v>322</v>
-      </c>
-      <c r="J61">
-        <v>1</v>
-      </c>
-      <c r="K61" t="s">
-        <v>22</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61" t="s">
-        <v>38</v>
-      </c>
-      <c r="N61" t="s">
-        <v>311</v>
-      </c>
-      <c r="O61" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -4714,28 +4726,28 @@
         <v>325</v>
       </c>
       <c r="B62" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C62" t="s">
         <v>102</v>
       </c>
       <c r="D62" t="s">
+        <v>326</v>
+      </c>
+      <c r="E62" t="s">
+        <v>321</v>
+      </c>
+      <c r="F62" t="s">
+        <v>326</v>
+      </c>
+      <c r="G62" t="s">
+        <v>321</v>
+      </c>
+      <c r="H62" t="s">
         <v>327</v>
       </c>
-      <c r="E62" t="s">
-        <v>328</v>
-      </c>
-      <c r="F62" t="s">
-        <v>327</v>
-      </c>
-      <c r="G62" t="s">
-        <v>328</v>
-      </c>
-      <c r="H62" t="s">
-        <v>329</v>
-      </c>
       <c r="I62" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="J62">
         <v>3</v>
@@ -4750,39 +4762,39 @@
         <v>23</v>
       </c>
       <c r="N62" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="O62" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B63" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C63" t="s">
         <v>102</v>
       </c>
       <c r="D63" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E63" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F63" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G63" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H63" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I63" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -4797,39 +4809,39 @@
         <v>23</v>
       </c>
       <c r="N63" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="O63" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B64" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C64" t="s">
         <v>102</v>
       </c>
       <c r="D64" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E64" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F64" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G64" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H64" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I64" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="J64">
         <v>3</v>
@@ -4844,86 +4856,86 @@
         <v>23</v>
       </c>
       <c r="N64" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="O64" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>334</v>
+      </c>
+      <c r="B65" t="s">
+        <v>335</v>
+      </c>
+      <c r="C65" t="s">
+        <v>336</v>
+      </c>
+      <c r="D65" t="s">
+        <v>337</v>
+      </c>
+      <c r="E65" t="s">
         <v>338</v>
       </c>
-      <c r="B65" t="s">
-        <v>326</v>
-      </c>
-      <c r="C65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>337</v>
+      </c>
+      <c r="G65" t="s">
+        <v>338</v>
+      </c>
+      <c r="H65" t="s">
         <v>339</v>
       </c>
-      <c r="E65" t="s">
-        <v>328</v>
-      </c>
-      <c r="F65" t="s">
-        <v>339</v>
-      </c>
-      <c r="G65" t="s">
-        <v>328</v>
-      </c>
-      <c r="H65" t="s">
-        <v>340</v>
-      </c>
       <c r="I65" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K65" t="s">
         <v>22</v>
       </c>
       <c r="L65">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M65" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="N65" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="O65" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>340</v>
+      </c>
+      <c r="B66" t="s">
+        <v>335</v>
+      </c>
+      <c r="C66" t="s">
+        <v>336</v>
+      </c>
+      <c r="D66" t="s">
         <v>341</v>
       </c>
-      <c r="B66" t="s">
+      <c r="E66" t="s">
         <v>342</v>
       </c>
-      <c r="C66" t="s">
+      <c r="F66" t="s">
+        <v>341</v>
+      </c>
+      <c r="G66" t="s">
+        <v>342</v>
+      </c>
+      <c r="H66" t="s">
+        <v>341</v>
+      </c>
+      <c r="I66" t="s">
         <v>343</v>
-      </c>
-      <c r="D66" t="s">
-        <v>344</v>
-      </c>
-      <c r="E66" t="s">
-        <v>345</v>
-      </c>
-      <c r="F66" t="s">
-        <v>344</v>
-      </c>
-      <c r="G66" t="s">
-        <v>345</v>
-      </c>
-      <c r="H66" t="s">
-        <v>346</v>
-      </c>
-      <c r="I66" t="s">
-        <v>345</v>
       </c>
       <c r="J66">
         <v>6</v>
@@ -4932,45 +4944,45 @@
         <v>22</v>
       </c>
       <c r="L66">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M66" t="s">
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O66" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B67" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C67" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D67" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="E67" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F67" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G67" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H67" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="I67" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J67">
         <v>6</v>
@@ -4985,86 +4997,86 @@
         <v>38</v>
       </c>
       <c r="N67" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O67" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>347</v>
+      </c>
+      <c r="B68" t="s">
+        <v>348</v>
+      </c>
+      <c r="C68" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" t="s">
+        <v>350</v>
+      </c>
+      <c r="E68" t="s">
         <v>351</v>
       </c>
-      <c r="B68" t="s">
-        <v>342</v>
-      </c>
-      <c r="C68" t="s">
-        <v>343</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="F68" t="s">
+        <v>350</v>
+      </c>
+      <c r="G68" t="s">
+        <v>351</v>
+      </c>
+      <c r="H68" t="s">
+        <v>350</v>
+      </c>
+      <c r="I68" t="s">
+        <v>352</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="K68" t="s">
+        <v>22</v>
+      </c>
+      <c r="L68">
+        <v>270</v>
+      </c>
+      <c r="M68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" t="s">
         <v>348</v>
       </c>
-      <c r="E68" t="s">
-        <v>352</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="O68" t="s">
         <v>348</v>
-      </c>
-      <c r="G68" t="s">
-        <v>352</v>
-      </c>
-      <c r="H68" t="s">
-        <v>348</v>
-      </c>
-      <c r="I68" t="s">
-        <v>353</v>
-      </c>
-      <c r="J68">
-        <v>6</v>
-      </c>
-      <c r="K68" t="s">
-        <v>22</v>
-      </c>
-      <c r="L68">
-        <v>90</v>
-      </c>
-      <c r="M68" t="s">
-        <v>38</v>
-      </c>
-      <c r="N68" t="s">
-        <v>342</v>
-      </c>
-      <c r="O68" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>353</v>
+      </c>
+      <c r="B69" t="s">
+        <v>348</v>
+      </c>
+      <c r="C69" t="s">
+        <v>349</v>
+      </c>
+      <c r="D69" t="s">
         <v>354</v>
       </c>
-      <c r="B69" t="s">
-        <v>355</v>
-      </c>
-      <c r="C69" t="s">
-        <v>356</v>
-      </c>
-      <c r="D69" t="s">
-        <v>357</v>
-      </c>
       <c r="E69" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="F69" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G69" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="H69" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I69" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="J69">
         <v>2</v>
@@ -5079,86 +5091,86 @@
         <v>23</v>
       </c>
       <c r="N69" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="O69" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>355</v>
+      </c>
+      <c r="B70" t="s">
+        <v>356</v>
+      </c>
+      <c r="C70" t="s">
+        <v>357</v>
+      </c>
+      <c r="D70" t="s">
+        <v>358</v>
+      </c>
+      <c r="E70" t="s">
+        <v>264</v>
+      </c>
+      <c r="F70" t="s">
+        <v>358</v>
+      </c>
+      <c r="G70" t="s">
+        <v>264</v>
+      </c>
+      <c r="H70" t="s">
+        <v>359</v>
+      </c>
+      <c r="I70" t="s">
+        <v>264</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="K70" t="s">
+        <v>22</v>
+      </c>
+      <c r="L70">
+        <v>180</v>
+      </c>
+      <c r="M70" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" t="s">
         <v>360</v>
       </c>
-      <c r="B70" t="s">
-        <v>355</v>
-      </c>
-      <c r="C70" t="s">
-        <v>356</v>
-      </c>
-      <c r="D70" t="s">
-        <v>361</v>
-      </c>
-      <c r="E70" t="s">
-        <v>358</v>
-      </c>
-      <c r="F70" t="s">
-        <v>361</v>
-      </c>
-      <c r="G70" t="s">
-        <v>358</v>
-      </c>
-      <c r="H70" t="s">
-        <v>361</v>
-      </c>
-      <c r="I70" t="s">
-        <v>359</v>
-      </c>
-      <c r="J70">
-        <v>2</v>
-      </c>
-      <c r="K70" t="s">
-        <v>22</v>
-      </c>
-      <c r="L70">
-        <v>270</v>
-      </c>
-      <c r="M70" t="s">
-        <v>23</v>
-      </c>
-      <c r="N70" t="s">
-        <v>355</v>
-      </c>
       <c r="O70" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>361</v>
+      </c>
+      <c r="B71" t="s">
+        <v>356</v>
+      </c>
+      <c r="C71" t="s">
+        <v>357</v>
+      </c>
+      <c r="D71" t="s">
+        <v>358</v>
+      </c>
+      <c r="E71" t="s">
         <v>362</v>
       </c>
-      <c r="B71" t="s">
-        <v>363</v>
-      </c>
-      <c r="C71" t="s">
-        <v>364</v>
-      </c>
-      <c r="D71" t="s">
-        <v>365</v>
-      </c>
-      <c r="E71" t="s">
-        <v>271</v>
-      </c>
       <c r="F71" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="G71" t="s">
-        <v>271</v>
+        <v>362</v>
       </c>
       <c r="H71" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="I71" t="s">
-        <v>271</v>
+        <v>362</v>
       </c>
       <c r="J71">
         <v>2</v>
@@ -5173,39 +5185,39 @@
         <v>23</v>
       </c>
       <c r="N71" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="O71" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B72" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C72" t="s">
-        <v>364</v>
+        <v>91</v>
       </c>
       <c r="D72" t="s">
         <v>365</v>
       </c>
       <c r="E72" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F72" t="s">
         <v>365</v>
       </c>
       <c r="G72" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H72" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I72" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J72">
         <v>2</v>
@@ -5214,45 +5226,45 @@
         <v>22</v>
       </c>
       <c r="L72">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M72" t="s">
         <v>23</v>
       </c>
       <c r="N72" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="O72" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B73" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C73" t="s">
         <v>91</v>
       </c>
       <c r="D73" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E73" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="F73" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G73" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="H73" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I73" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="J73">
         <v>2</v>
@@ -5267,39 +5279,39 @@
         <v>23</v>
       </c>
       <c r="N73" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="O73" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B74" t="s">
         <v>371</v>
       </c>
       <c r="C74" t="s">
-        <v>91</v>
+        <v>357</v>
       </c>
       <c r="D74" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E74" t="s">
         <v>373</v>
       </c>
       <c r="F74" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G74" t="s">
         <v>373</v>
       </c>
       <c r="H74" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="I74" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J74">
         <v>2</v>
@@ -5308,45 +5320,45 @@
         <v>22</v>
       </c>
       <c r="L74">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M74" t="s">
         <v>23</v>
       </c>
       <c r="N74" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="O74" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>376</v>
+      </c>
+      <c r="B75" t="s">
+        <v>371</v>
+      </c>
+      <c r="C75" t="s">
+        <v>357</v>
+      </c>
+      <c r="D75" t="s">
         <v>377</v>
       </c>
-      <c r="B75" t="s">
+      <c r="E75" t="s">
+        <v>373</v>
+      </c>
+      <c r="F75" t="s">
+        <v>377</v>
+      </c>
+      <c r="G75" t="s">
+        <v>373</v>
+      </c>
+      <c r="H75" t="s">
         <v>378</v>
       </c>
-      <c r="C75" t="s">
-        <v>364</v>
-      </c>
-      <c r="D75" t="s">
-        <v>379</v>
-      </c>
-      <c r="E75" t="s">
-        <v>380</v>
-      </c>
-      <c r="F75" t="s">
-        <v>379</v>
-      </c>
-      <c r="G75" t="s">
-        <v>380</v>
-      </c>
-      <c r="H75" t="s">
-        <v>381</v>
-      </c>
       <c r="I75" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="J75">
         <v>2</v>
@@ -5355,45 +5367,45 @@
         <v>22</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M75" t="s">
         <v>23</v>
       </c>
       <c r="N75" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="O75" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B76" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C76" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D76" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E76" t="s">
+        <v>373</v>
+      </c>
+      <c r="F76" t="s">
         <v>380</v>
       </c>
-      <c r="F76" t="s">
-        <v>384</v>
-      </c>
       <c r="G76" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="H76" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="I76" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="J76">
         <v>2</v>
@@ -5408,39 +5420,39 @@
         <v>23</v>
       </c>
       <c r="N76" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="O76" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B77" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C77" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D77" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E77" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F77" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G77" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="H77" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="I77" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="J77">
         <v>2</v>
@@ -5449,95 +5461,95 @@
         <v>22</v>
       </c>
       <c r="L77">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M77" t="s">
         <v>23</v>
       </c>
       <c r="N77" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="O77" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>385</v>
+      </c>
+      <c r="B78" t="s">
+        <v>386</v>
+      </c>
+      <c r="C78" t="s">
+        <v>387</v>
+      </c>
+      <c r="D78" t="s">
+        <v>365</v>
+      </c>
+      <c r="E78" t="s">
+        <v>388</v>
+      </c>
+      <c r="F78" t="s">
+        <v>365</v>
+      </c>
+      <c r="G78" t="s">
+        <v>388</v>
+      </c>
+      <c r="H78" t="s">
         <v>389</v>
       </c>
-      <c r="B78" t="s">
-        <v>378</v>
-      </c>
-      <c r="C78" t="s">
-        <v>364</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="I78" t="s">
         <v>390</v>
       </c>
-      <c r="E78" t="s">
-        <v>380</v>
-      </c>
-      <c r="F78" t="s">
-        <v>390</v>
-      </c>
-      <c r="G78" t="s">
-        <v>380</v>
-      </c>
-      <c r="H78" t="s">
-        <v>391</v>
-      </c>
-      <c r="I78" t="s">
-        <v>380</v>
-      </c>
       <c r="J78">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K78" t="s">
         <v>22</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M78" t="s">
         <v>23</v>
       </c>
       <c r="N78" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="O78" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>391</v>
+      </c>
+      <c r="B79" t="s">
         <v>392</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>393</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>394</v>
       </c>
-      <c r="D79" t="s">
-        <v>372</v>
-      </c>
       <c r="E79" t="s">
+        <v>93</v>
+      </c>
+      <c r="F79" t="s">
+        <v>394</v>
+      </c>
+      <c r="G79" t="s">
+        <v>93</v>
+      </c>
+      <c r="H79" t="s">
         <v>395</v>
       </c>
-      <c r="F79" t="s">
-        <v>372</v>
-      </c>
-      <c r="G79" t="s">
-        <v>395</v>
-      </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>396</v>
       </c>
-      <c r="I79" t="s">
-        <v>397</v>
-      </c>
       <c r="J79">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K79" t="s">
         <v>22</v>
@@ -5549,33 +5561,33 @@
         <v>23</v>
       </c>
       <c r="N79" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O79" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>397</v>
+      </c>
+      <c r="B80" t="s">
         <v>398</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>399</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>400</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>401</v>
       </c>
-      <c r="E80" t="s">
-        <v>93</v>
-      </c>
       <c r="F80" t="s">
+        <v>400</v>
+      </c>
+      <c r="G80" t="s">
         <v>401</v>
-      </c>
-      <c r="G80" t="s">
-        <v>93</v>
       </c>
       <c r="H80" t="s">
         <v>402</v>
@@ -5584,22 +5596,22 @@
         <v>403</v>
       </c>
       <c r="J80">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K80" t="s">
         <v>22</v>
       </c>
       <c r="L80">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M80" t="s">
         <v>23</v>
       </c>
       <c r="N80" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O80" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
@@ -5607,51 +5619,51 @@
         <v>404</v>
       </c>
       <c r="B81" t="s">
+        <v>250</v>
+      </c>
+      <c r="C81" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" t="s">
         <v>405</v>
       </c>
-      <c r="C81" t="s">
+      <c r="E81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F81" t="s">
+        <v>405</v>
+      </c>
+      <c r="G81" t="s">
+        <v>69</v>
+      </c>
+      <c r="H81" t="s">
         <v>406</v>
       </c>
-      <c r="D81" t="s">
-        <v>407</v>
-      </c>
-      <c r="E81" t="s">
-        <v>408</v>
-      </c>
-      <c r="F81" t="s">
-        <v>407</v>
-      </c>
-      <c r="G81" t="s">
-        <v>408</v>
-      </c>
-      <c r="H81" t="s">
-        <v>409</v>
-      </c>
       <c r="I81" t="s">
-        <v>410</v>
+        <v>69</v>
       </c>
       <c r="J81">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K81" t="s">
         <v>22</v>
       </c>
       <c r="L81">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M81" t="s">
         <v>23</v>
       </c>
       <c r="N81" t="s">
-        <v>405</v>
+        <v>253</v>
       </c>
       <c r="O81" t="s">
-        <v>405</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B82" t="s">
         <v>250</v>
@@ -5660,22 +5672,22 @@
         <v>91</v>
       </c>
       <c r="D82" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="E82" t="s">
-        <v>69</v>
+        <v>247</v>
       </c>
       <c r="F82" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="G82" t="s">
-        <v>69</v>
+        <v>247</v>
       </c>
       <c r="H82" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="I82" t="s">
-        <v>69</v>
+        <v>247</v>
       </c>
       <c r="J82">
         <v>2</v>
@@ -5698,31 +5710,31 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B83" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="C83" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E83" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="F83" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G83" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="H83" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I83" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="J83">
         <v>2</v>
@@ -5731,48 +5743,48 @@
         <v>22</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M83" t="s">
         <v>23</v>
       </c>
       <c r="N83" t="s">
-        <v>253</v>
+        <v>179</v>
       </c>
       <c r="O83" t="s">
-        <v>253</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>411</v>
+      </c>
+      <c r="B84" t="s">
+        <v>412</v>
+      </c>
+      <c r="C84" t="s">
+        <v>413</v>
+      </c>
+      <c r="D84" t="s">
+        <v>414</v>
+      </c>
+      <c r="E84" t="s">
         <v>415</v>
       </c>
-      <c r="B84" t="s">
-        <v>175</v>
-      </c>
-      <c r="C84" t="s">
-        <v>26</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="F84" t="s">
+        <v>414</v>
+      </c>
+      <c r="G84" t="s">
+        <v>415</v>
+      </c>
+      <c r="H84" t="s">
         <v>416</v>
       </c>
-      <c r="E84" t="s">
-        <v>216</v>
-      </c>
-      <c r="F84" t="s">
-        <v>416</v>
-      </c>
-      <c r="G84" t="s">
-        <v>216</v>
-      </c>
-      <c r="H84" t="s">
-        <v>417</v>
-      </c>
       <c r="I84" t="s">
-        <v>216</v>
+        <v>415</v>
       </c>
       <c r="J84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K84" t="s">
         <v>22</v>
@@ -5781,42 +5793,42 @@
         <v>180</v>
       </c>
       <c r="M84" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="N84" t="s">
-        <v>179</v>
+        <v>412</v>
       </c>
       <c r="O84" t="s">
-        <v>179</v>
+        <v>412</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>417</v>
+      </c>
+      <c r="B85" t="s">
+        <v>412</v>
+      </c>
+      <c r="C85" t="s">
+        <v>413</v>
+      </c>
+      <c r="D85" t="s">
+        <v>108</v>
+      </c>
+      <c r="E85" t="s">
         <v>418</v>
       </c>
-      <c r="B85" t="s">
-        <v>419</v>
-      </c>
-      <c r="C85" t="s">
-        <v>420</v>
-      </c>
-      <c r="D85" t="s">
-        <v>421</v>
-      </c>
-      <c r="E85" t="s">
-        <v>422</v>
-      </c>
       <c r="F85" t="s">
-        <v>421</v>
+        <v>108</v>
       </c>
       <c r="G85" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H85" t="s">
-        <v>423</v>
+        <v>243</v>
       </c>
       <c r="I85" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="J85">
         <v>3</v>
@@ -5825,68 +5837,68 @@
         <v>22</v>
       </c>
       <c r="L85">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M85" t="s">
         <v>38</v>
       </c>
       <c r="N85" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="O85" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B86" t="s">
-        <v>419</v>
+        <v>250</v>
       </c>
       <c r="C86" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" t="s">
         <v>420</v>
       </c>
-      <c r="D86" t="s">
-        <v>108</v>
-      </c>
       <c r="E86" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F86" t="s">
-        <v>108</v>
+        <v>420</v>
       </c>
       <c r="G86" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H86" t="s">
-        <v>243</v>
+        <v>422</v>
       </c>
       <c r="I86" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="J86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K86" t="s">
         <v>22</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M86" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N86" t="s">
-        <v>419</v>
+        <v>253</v>
       </c>
       <c r="O86" t="s">
-        <v>419</v>
+        <v>253</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B87" t="s">
         <v>250</v>
@@ -5895,22 +5907,22 @@
         <v>91</v>
       </c>
       <c r="D87" t="s">
-        <v>427</v>
+        <v>127</v>
       </c>
       <c r="E87" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F87" t="s">
-        <v>427</v>
+        <v>127</v>
       </c>
       <c r="G87" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="H87" t="s">
-        <v>429</v>
+        <v>128</v>
       </c>
       <c r="I87" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="J87">
         <v>2</v>
@@ -5933,31 +5945,31 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B88" t="s">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="C88" t="s">
         <v>91</v>
       </c>
       <c r="D88" t="s">
-        <v>127</v>
+        <v>426</v>
       </c>
       <c r="E88" t="s">
+        <v>427</v>
+      </c>
+      <c r="F88" t="s">
+        <v>426</v>
+      </c>
+      <c r="G88" t="s">
+        <v>427</v>
+      </c>
+      <c r="H88" t="s">
         <v>428</v>
       </c>
-      <c r="F88" t="s">
-        <v>127</v>
-      </c>
-      <c r="G88" t="s">
-        <v>428</v>
-      </c>
-      <c r="H88" t="s">
-        <v>128</v>
-      </c>
       <c r="I88" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J88">
         <v>2</v>
@@ -5966,45 +5978,45 @@
         <v>22</v>
       </c>
       <c r="L88">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="M88" t="s">
         <v>23</v>
       </c>
       <c r="N88" t="s">
-        <v>253</v>
+        <v>52</v>
       </c>
       <c r="O88" t="s">
-        <v>253</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C89" t="s">
         <v>91</v>
       </c>
       <c r="D89" t="s">
+        <v>431</v>
+      </c>
+      <c r="E89" t="s">
+        <v>432</v>
+      </c>
+      <c r="F89" t="s">
+        <v>431</v>
+      </c>
+      <c r="G89" t="s">
+        <v>432</v>
+      </c>
+      <c r="H89" t="s">
         <v>433</v>
       </c>
-      <c r="E89" t="s">
-        <v>434</v>
-      </c>
-      <c r="F89" t="s">
-        <v>433</v>
-      </c>
-      <c r="G89" t="s">
-        <v>434</v>
-      </c>
-      <c r="H89" t="s">
-        <v>435</v>
-      </c>
       <c r="I89" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="J89">
         <v>2</v>
@@ -6013,7 +6025,7 @@
         <v>22</v>
       </c>
       <c r="L89">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="M89" t="s">
         <v>23</v>
@@ -6027,31 +6039,31 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B90" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C90" t="s">
         <v>91</v>
       </c>
       <c r="D90" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E90" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F90" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G90" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H90" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="I90" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J90">
         <v>2</v>
@@ -6060,7 +6072,7 @@
         <v>22</v>
       </c>
       <c r="L90">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M90" t="s">
         <v>23</v>
@@ -6074,31 +6086,31 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B91" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C91" t="s">
         <v>91</v>
       </c>
       <c r="D91" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E91" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="F91" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G91" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="H91" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I91" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="J91">
         <v>2</v>
@@ -6107,7 +6119,7 @@
         <v>22</v>
       </c>
       <c r="L91">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M91" t="s">
         <v>23</v>
@@ -6121,31 +6133,31 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B92" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C92" t="s">
         <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E92" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="F92" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G92" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="H92" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="I92" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="J92">
         <v>2</v>
@@ -6154,7 +6166,7 @@
         <v>22</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M92" t="s">
         <v>23</v>
@@ -6168,78 +6180,78 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B93" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="C93" t="s">
         <v>91</v>
       </c>
       <c r="D93" t="s">
+        <v>114</v>
+      </c>
+      <c r="E93" t="s">
+        <v>447</v>
+      </c>
+      <c r="F93" t="s">
+        <v>114</v>
+      </c>
+      <c r="G93" t="s">
+        <v>447</v>
+      </c>
+      <c r="H93" t="s">
+        <v>448</v>
+      </c>
+      <c r="I93" t="s">
+        <v>447</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93" t="s">
+        <v>22</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" t="s">
         <v>449</v>
       </c>
-      <c r="E93" t="s">
-        <v>450</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="O93" t="s">
         <v>449</v>
-      </c>
-      <c r="G93" t="s">
-        <v>450</v>
-      </c>
-      <c r="H93" t="s">
-        <v>449</v>
-      </c>
-      <c r="I93" t="s">
-        <v>451</v>
-      </c>
-      <c r="J93">
-        <v>2</v>
-      </c>
-      <c r="K93" t="s">
-        <v>22</v>
-      </c>
-      <c r="L93">
-        <v>270</v>
-      </c>
-      <c r="M93" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" t="s">
-        <v>52</v>
-      </c>
-      <c r="O93" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B94" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C94" t="s">
         <v>91</v>
       </c>
       <c r="D94" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="E94" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F94" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="G94" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H94" t="s">
-        <v>455</v>
+        <v>187</v>
       </c>
       <c r="I94" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J94">
         <v>2</v>
@@ -6254,39 +6266,39 @@
         <v>23</v>
       </c>
       <c r="N94" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O94" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B95" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C95" t="s">
         <v>91</v>
       </c>
       <c r="D95" t="s">
-        <v>185</v>
+        <v>455</v>
       </c>
       <c r="E95" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F95" t="s">
-        <v>185</v>
+        <v>455</v>
       </c>
       <c r="G95" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H95" t="s">
-        <v>187</v>
+        <v>455</v>
       </c>
       <c r="I95" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J95">
         <v>2</v>
@@ -6295,46 +6307,46 @@
         <v>22</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M95" t="s">
         <v>23</v>
       </c>
       <c r="N95" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="O95" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B96" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C96" t="s">
         <v>91</v>
       </c>
       <c r="D96" t="s">
+        <v>459</v>
+      </c>
+      <c r="E96" t="s">
+        <v>460</v>
+      </c>
+      <c r="F96" t="s">
+        <v>459</v>
+      </c>
+      <c r="G96" t="s">
+        <v>460</v>
+      </c>
+      <c r="H96" t="s">
+        <v>461</v>
+      </c>
+      <c r="I96" t="s">
         <v>462</v>
       </c>
-      <c r="E96" t="s">
-        <v>463</v>
-      </c>
-      <c r="F96" t="s">
-        <v>462</v>
-      </c>
-      <c r="G96" t="s">
-        <v>463</v>
-      </c>
-      <c r="H96" t="s">
-        <v>462</v>
-      </c>
-      <c r="I96" t="s">
-        <v>464</v>
-      </c>
       <c r="J96">
         <v>2</v>
       </c>
@@ -6342,45 +6354,45 @@
         <v>22</v>
       </c>
       <c r="L96">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="M96" t="s">
         <v>23</v>
       </c>
       <c r="N96" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="O96" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B97" t="s">
-        <v>453</v>
+        <v>250</v>
       </c>
       <c r="C97" t="s">
         <v>91</v>
       </c>
       <c r="D97" t="s">
+        <v>464</v>
+      </c>
+      <c r="E97" t="s">
+        <v>465</v>
+      </c>
+      <c r="F97" t="s">
+        <v>464</v>
+      </c>
+      <c r="G97" t="s">
+        <v>465</v>
+      </c>
+      <c r="H97" t="s">
         <v>466</v>
       </c>
-      <c r="E97" t="s">
-        <v>467</v>
-      </c>
-      <c r="F97" t="s">
-        <v>466</v>
-      </c>
-      <c r="G97" t="s">
-        <v>467</v>
-      </c>
-      <c r="H97" t="s">
-        <v>468</v>
-      </c>
       <c r="I97" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -6389,21 +6401,21 @@
         <v>22</v>
       </c>
       <c r="L97">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="M97" t="s">
         <v>23</v>
       </c>
       <c r="N97" t="s">
-        <v>456</v>
+        <v>253</v>
       </c>
       <c r="O97" t="s">
-        <v>456</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B98" t="s">
         <v>250</v>
@@ -6412,22 +6424,22 @@
         <v>91</v>
       </c>
       <c r="D98" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E98" t="s">
-        <v>472</v>
+        <v>247</v>
       </c>
       <c r="F98" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G98" t="s">
-        <v>472</v>
+        <v>247</v>
       </c>
       <c r="H98" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I98" t="s">
-        <v>472</v>
+        <v>247</v>
       </c>
       <c r="J98">
         <v>2</v>
@@ -6436,7 +6448,7 @@
         <v>22</v>
       </c>
       <c r="L98">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M98" t="s">
         <v>23</v>
@@ -6450,96 +6462,143 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>470</v>
+      </c>
+      <c r="B99" t="s">
+        <v>471</v>
+      </c>
+      <c r="C99" t="s">
+        <v>472</v>
+      </c>
+      <c r="D99" t="s">
+        <v>473</v>
+      </c>
+      <c r="E99" t="s">
+        <v>465</v>
+      </c>
+      <c r="F99" t="s">
+        <v>473</v>
+      </c>
+      <c r="G99" t="s">
+        <v>465</v>
+      </c>
+      <c r="H99" t="s">
         <v>474</v>
       </c>
-      <c r="B99" t="s">
-        <v>250</v>
-      </c>
-      <c r="C99" t="s">
-        <v>91</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="I99" t="s">
         <v>475</v>
       </c>
-      <c r="E99" t="s">
-        <v>247</v>
-      </c>
-      <c r="F99" t="s">
-        <v>475</v>
-      </c>
-      <c r="G99" t="s">
-        <v>247</v>
-      </c>
-      <c r="H99" t="s">
-        <v>476</v>
-      </c>
-      <c r="I99" t="s">
-        <v>247</v>
-      </c>
       <c r="J99">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K99" t="s">
         <v>22</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M99" t="s">
         <v>23</v>
       </c>
       <c r="N99" t="s">
-        <v>253</v>
+        <v>471</v>
       </c>
       <c r="O99" t="s">
-        <v>253</v>
+        <v>471</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>476</v>
+      </c>
+      <c r="B100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" t="s">
+        <v>48</v>
+      </c>
+      <c r="D100" t="s">
         <v>477</v>
       </c>
-      <c r="B100" t="s">
+      <c r="E100" t="s">
         <v>478</v>
       </c>
-      <c r="C100" t="s">
+      <c r="F100" t="s">
+        <v>477</v>
+      </c>
+      <c r="G100" t="s">
+        <v>478</v>
+      </c>
+      <c r="H100" t="s">
         <v>479</v>
       </c>
-      <c r="D100" t="s">
+      <c r="I100" t="s">
+        <v>478</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100" t="s">
+        <v>22</v>
+      </c>
+      <c r="L100">
+        <v>180</v>
+      </c>
+      <c r="M100" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" t="s">
+        <v>52</v>
+      </c>
+      <c r="O100" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>480</v>
       </c>
-      <c r="E100" t="s">
-        <v>472</v>
-      </c>
-      <c r="F100" t="s">
-        <v>480</v>
-      </c>
-      <c r="G100" t="s">
-        <v>472</v>
-      </c>
-      <c r="H100" t="s">
+      <c r="B101" t="s">
         <v>481</v>
       </c>
-      <c r="I100" t="s">
+      <c r="C101" t="s">
         <v>482</v>
       </c>
-      <c r="J100">
-        <v>5</v>
-      </c>
-      <c r="K100" t="s">
-        <v>22</v>
-      </c>
-      <c r="L100">
+      <c r="D101" t="s">
+        <v>483</v>
+      </c>
+      <c r="E101" t="s">
+        <v>108</v>
+      </c>
+      <c r="F101" t="s">
+        <v>483</v>
+      </c>
+      <c r="G101" t="s">
+        <v>108</v>
+      </c>
+      <c r="H101" t="s">
+        <v>484</v>
+      </c>
+      <c r="I101" t="s">
+        <v>485</v>
+      </c>
+      <c r="J101">
+        <v>6</v>
+      </c>
+      <c r="K101" t="s">
+        <v>22</v>
+      </c>
+      <c r="L101">
         <v>90</v>
       </c>
-      <c r="M100" t="s">
-        <v>23</v>
-      </c>
-      <c r="N100" t="s">
-        <v>478</v>
-      </c>
-      <c r="O100" t="s">
-        <v>478</v>
+      <c r="M101" t="s">
+        <v>23</v>
+      </c>
+      <c r="N101" t="s">
+        <v>486</v>
+      </c>
+      <c r="O101" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
